--- a/docs/design-docs/11_プログラム設計書_組織・カレンダー・保守部品.xlsx
+++ b/docs/design-docs/11_プログラム設計書_組織・カレンダー・保守部品.xlsx
@@ -13,7 +13,605 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 部署マスタ管理</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>組織管理</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-ORG-DEPT</t>
+  </si>
+  <si>
+    <t>プログラム名</t>
+  </si>
+  <si>
+    <t>部署マスタ管理</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-ORG-DEPT</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>プログラム概要</t>
+  </si>
+  <si>
+    <t>部署master一覧(4階層tree表示)、登録・編集、統廃合履歴管理。上位部署tree Popup選択。過去日異動警告。</t>
+  </si>
+  <si>
+    <t>入出力定義</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>Formプロパティ</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>部署名</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>deptName</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>上位部署</t>
+  </si>
+  <si>
+    <t>parentDept</t>
+  </si>
+  <si>
+    <t>Popup</t>
+  </si>
+  <si>
+    <t>有効開始日</t>
+  </si>
+  <si>
+    <t>startDate</t>
+  </si>
+  <si>
+    <t>部署種別</t>
+  </si>
+  <si>
+    <t>deptType</t>
+  </si>
+  <si>
+    <t>処理詳細</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>処理内容</t>
+  </si>
+  <si>
+    <t>関連DAO</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>tree表示:4階層再帰構築(階層=indent幅)</t>
+  </si>
+  <si>
+    <t>DeptDao.findAll()</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>登録:code自動採番→INSERT</t>
+  </si>
+  <si>
+    <t>DeptDao.insert()</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>過去日異動check:開始日&amp;lt;本日→警告(保存可)</t>
+  </si>
+  <si>
+    <t>入力検証ルール</t>
+  </si>
+  <si>
+    <t>対象項目</t>
+  </si>
+  <si>
+    <t>検証ルール</t>
+  </si>
+  <si>
+    <t>エラーメッセージ(ja)</t>
+  </si>
+  <si>
+    <t>空不可 重複不可</t>
+  </si>
+  <si>
+    <t>endDate</t>
+  </si>
+  <si>
+    <t>startDate&amp;lt;endDate</t>
+  </si>
+  <si>
+    <t>状態遷移</t>
+  </si>
+  <si>
+    <t>遷移元</t>
+  </si>
+  <si>
+    <t>遷移先</t>
+  </si>
+  <si>
+    <t>トリガー</t>
+  </si>
+  <si>
+    <t>一覧</t>
+  </si>
+  <si>
+    <t>編集</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>子部署追加</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>tree Popup</t>
+  </si>
+  <si>
+    <t>上位部署選択</t>
+  </si>
+  <si>
+    <t>struts-config.xml</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>action path</t>
+  </si>
+  <si>
+    <t>/org/dept/*</t>
+  </si>
+  <si>
+    <t>action class</t>
+  </si>
+  <si>
+    <t>DeptListAction / DeptSaveAction</t>
+  </si>
+  <si>
+    <t>form bean</t>
+  </si>
+  <si>
+    <t>DeptSearchForm / DeptForm</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 担当者マスタ管理</t>
+  </si>
+  <si>
+    <t>PG-ORG-EMP</t>
+  </si>
+  <si>
+    <t>担当者マスタ管理</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-ORG-EMP</t>
+  </si>
+  <si>
+    <t>担当者master一覧(複合検索)、登録・編集(5section大form)。資格毎期限管理。loginID重複check。password SHA-256。</t>
+  </si>
+  <si>
+    <t>氏名</t>
+  </si>
+  <si>
+    <t>empName</t>
+  </si>
+  <si>
+    <t>フリガナ</t>
+  </si>
+  <si>
+    <t>empKana</t>
+  </si>
+  <si>
+    <t>katakana</t>
+  </si>
+  <si>
+    <t>部署</t>
+  </si>
+  <si>
+    <t>empDept</t>
+  </si>
+  <si>
+    <t>保有資格[]</t>
+  </si>
+  <si>
+    <t>String[]</t>
+  </si>
+  <si>
+    <t>empQual</t>
+  </si>
+  <si>
+    <t>checkbox</t>
+  </si>
+  <si>
+    <t>点検員ランク</t>
+  </si>
+  <si>
+    <t>insRank</t>
+  </si>
+  <si>
+    <t>認定有効期限</t>
+  </si>
+  <si>
+    <t>insExpire</t>
+  </si>
+  <si>
+    <t>loginID</t>
+  </si>
+  <si>
+    <t>loginId</t>
+  </si>
+  <si>
+    <t>重複不可</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>社員番号自動採番(EMP-NNNN)→5section Form</t>
+  </si>
+  <si>
+    <t>資格毎期限validation</t>
+  </si>
+  <si>
+    <t>条件付</t>
+  </si>
+  <si>
+    <t>loginID重複check</t>
+  </si>
+  <si>
+    <t>EmpDao.countByLoginId()</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>password:確認一致→SHA-256→保存</t>
+  </si>
+  <si>
+    <t>空不可</t>
+  </si>
+  <si>
+    <t>katakanaのみ</t>
+  </si>
+  <si>
+    <t>8文字以上</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>未来日</t>
+  </si>
+  <si>
+    <t>表示</t>
+  </si>
+  <si>
+    <t>5section編集</t>
+  </si>
+  <si>
+    <t>保存→一覧</t>
+  </si>
+  <si>
+    <t>保存</t>
+  </si>
+  <si>
+    <t>error→再表示</t>
+  </si>
+  <si>
+    <t>保存→NG</t>
+  </si>
+  <si>
+    <t>/org/emp/*</t>
+  </si>
+  <si>
+    <t>EmpListAction / EmpSaveAction</t>
+  </si>
+  <si>
+    <t>EmpSearchForm / EmpForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 休日カレンダー管理</t>
+  </si>
+  <si>
+    <t>カレンダー管理</t>
+  </si>
+  <si>
+    <t>PG-CAL</t>
+  </si>
+  <si>
+    <t>休日カレンダー管理</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-CAL</t>
+  </si>
+  <si>
+    <t>休日calendar月別table表示(色分け)、範囲指定一括登録、重複check、振替出勤日設定。</t>
+  </si>
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>calYear</t>
+  </si>
+  <si>
+    <t>日付範囲from/to</t>
+  </si>
+  <si>
+    <t>calDateFrom/To</t>
+  </si>
+  <si>
+    <t>休日種別</t>
+  </si>
+  <si>
+    <t>calType</t>
+  </si>
+  <si>
+    <t>振替日</t>
+  </si>
+  <si>
+    <t>transferFrom/To</t>
+  </si>
+  <si>
+    <t>月別calendar描画:日付計算→曜日→週割→7列×5-6行</t>
+  </si>
+  <si>
+    <t>休日色分け:法定=赤 会社=青 停止=黄</t>
+  </si>
+  <si>
+    <t>CSS class</t>
+  </si>
+  <si>
+    <t>範囲一括登録:from〜to全date INSERT(重複→error)</t>
+  </si>
+  <si>
+    <t>CalDao.bulkInsert()</t>
+  </si>
+  <si>
+    <t>振替設定:休日→出勤日登録</t>
+  </si>
+  <si>
+    <t>from≦to</t>
+  </si>
+  <si>
+    <t>transferFrom</t>
+  </si>
+  <si>
+    <t>休日であること</t>
+  </si>
+  <si>
+    <t>transferTo</t>
+  </si>
+  <si>
+    <t>休日でないこと</t>
+  </si>
+  <si>
+    <t>月別calendar</t>
+  </si>
+  <si>
+    <t>年度選択→表示</t>
+  </si>
+  <si>
+    <t>登録/編集</t>
+  </si>
+  <si>
+    <t>日付click</t>
+  </si>
+  <si>
+    <t>登録</t>
+  </si>
+  <si>
+    <t>一括登録→一覧</t>
+  </si>
+  <si>
+    <t>一括登録</t>
+  </si>
+  <si>
+    <t>/cal/*</t>
+  </si>
+  <si>
+    <t>CalendarListAction / CalendarSaveAction</t>
+  </si>
+  <si>
+    <t>CalendarForm / CalendarRegForm</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 保守部品管理</t>
+  </si>
+  <si>
+    <t>保守部品管理</t>
+  </si>
+  <si>
+    <t>PG-PRT</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-PRT</t>
+  </si>
+  <si>
+    <t>保守部品一覧・登録・編集、使用実績管理。在庫alert(発注点下回)。適用設備checkbox tree選択。</t>
+  </si>
+  <si>
+    <t>部品名</t>
+  </si>
+  <si>
+    <t>prtName</t>
+  </si>
+  <si>
+    <t>部品種別</t>
+  </si>
+  <si>
+    <t>prtType</t>
+  </si>
+  <si>
+    <t>適用設備[]</t>
+  </si>
+  <si>
+    <t>prtEqp</t>
+  </si>
+  <si>
+    <t>checkbox tree</t>
+  </si>
+  <si>
+    <t>発注点</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>orderPoint</t>
+  </si>
+  <si>
+    <t>安全在庫数</t>
+  </si>
+  <si>
+    <t>safetyStock</t>
+  </si>
+  <si>
+    <t>単価</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>一覧:在庫&amp;lt;発注点→僅少badge(黄) =0→切badge(赤)</t>
+  </si>
+  <si>
+    <t>登録:適用設備tree→複数選択→保存</t>
+  </si>
+  <si>
+    <t>使用実績:点検/修繕→部品使用→在庫自動減算</t>
+  </si>
+  <si>
+    <t>PartsDao.updateStock()</t>
+  </si>
+  <si>
+    <t>在庫警告:使用後在庫≦発注点→alert</t>
+  </si>
+  <si>
+    <t>警告のみ</t>
+  </si>
+  <si>
+    <t>0以上</t>
+  </si>
+  <si>
+    <t>orderPoint&amp;gt;safetyStock</t>
+  </si>
+  <si>
+    <t>在庫alert表示</t>
+  </si>
+  <si>
+    <t>適用設備tree選択</t>
+  </si>
+  <si>
+    <t>使用実績</t>
+  </si>
+  <si>
+    <t>在庫自動減算→警告判定</t>
+  </si>
+  <si>
+    <t>/parts/*</t>
+  </si>
+  <si>
+    <t>PartsXxxAction</t>
+  </si>
+  <si>
+    <t>PartsXxxForm</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
